--- a/data/trans_dic/P56$familiarvive-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,18</t>
+          <t>0,0; 56,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,7; 74,42</t>
+          <t>9,5; 72,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,02</t>
+          <t>0,0; 66,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,04</t>
+          <t>0,0; 47,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,3; 49,19</t>
+          <t>12,62; 51,9</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,24</t>
+          <t>0,0; 65,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,87</t>
+          <t>0,0; 40,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,64; 49,06</t>
+          <t>4,85; 45,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,6</t>
+          <t>0,0; 64,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,64</t>
+          <t>0,0; 62,33</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,82; 32,61</t>
+          <t>3,55; 32,26</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,88</t>
+          <t>0,0; 60,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,95; 47,89</t>
+          <t>6,56; 47,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 41,04</t>
+          <t>4,74; 43,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,49</t>
+          <t>0,0; 58,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,62</t>
+          <t>14,64; 84,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 22,2</t>
+          <t>2,34; 22,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,39</t>
+          <t>0,0; 52,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 41,67</t>
+          <t>5,67; 41,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,19; 58,79</t>
+          <t>13,76; 57,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 25,4</t>
+          <t>6,23; 25,47</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 43,85</t>
+          <t>12,4; 42,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,47; 48,43</t>
+          <t>16,79; 48,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 33,66</t>
+          <t>6,38; 33,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 22,76</t>
+          <t>6,33; 22,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,38</t>
+          <t>0,0; 74,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,9; 46,06</t>
+          <t>6,01; 52,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,02; 49,71</t>
+          <t>6,35; 51,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,04; 38,29</t>
+          <t>14,72; 37,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,62; 42,55</t>
+          <t>13,55; 42,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,17; 41,71</t>
+          <t>17,24; 42,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 34,26</t>
+          <t>10,28; 34,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,85; 24,96</t>
+          <t>11,51; 25,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,28</t>
+          <t>0,0; 45,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 29,94</t>
+          <t>3,74; 32,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 24,9</t>
+          <t>2,78; 26,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,25; 63,18</t>
+          <t>13,85; 63,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,08; 42,15</t>
+          <t>18,66; 42,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,68; 48,29</t>
+          <t>16,11; 49,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,53; 25,41</t>
+          <t>13,06; 24,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,91; 49,09</t>
+          <t>13,3; 48,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 33,48</t>
+          <t>14,92; 34,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,85; 36,8</t>
+          <t>13,29; 36,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,33; 22,8</t>
+          <t>12,37; 22,47</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,75; 59,47</t>
+          <t>32,59; 59,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,81; 38,42</t>
+          <t>19,61; 39,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,78; 35,51</t>
+          <t>15,2; 35,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,99; 31,74</t>
+          <t>19,71; 31,94</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,75; 59,47</t>
+          <t>32,59; 59,4</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,81; 38,42</t>
+          <t>19,61; 39,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,78; 35,51</t>
+          <t>15,2; 35,13</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,67; 31,29</t>
+          <t>18,72; 31,1</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,93; 31,83</t>
+          <t>9,98; 31,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,0; 32,85</t>
+          <t>11,3; 32,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 27,03</t>
+          <t>9,8; 25,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 20,17</t>
+          <t>9,28; 20,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,8; 51,58</t>
+          <t>30,49; 51,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,81; 34,86</t>
+          <t>22,62; 35,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,06; 34,26</t>
+          <t>18,3; 33,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,57</t>
+          <t>18,2; 26,15</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>25,87; 41,88</t>
+          <t>26,57; 41,94</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,55; 31,8</t>
+          <t>20,61; 31,33</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17,91; 29,81</t>
+          <t>18,35; 30,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,25; 22,97</t>
+          <t>16,45; 22,75</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda un familiar conviviente cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3386</t>
+          <t>0; 3208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1033; 4344</t>
+          <t>555; 4223</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1351</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5090</t>
+          <t>0; 4996</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5573</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1191; 5685</t>
+          <t>1459; 5999</t>
         </is>
       </c>
     </row>
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4394</t>
+          <t>0; 4253</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3402</t>
+          <t>0; 3586</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1442</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,32 +2165,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>376; 3977</t>
+          <t>393; 3654</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1474</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5875</t>
+          <t>0; 6333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5767</t>
+          <t>0; 5831</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>644; 5499</t>
+          <t>599; 5438</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1393</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4177</t>
+          <t>0; 4324</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>724; 4995</t>
+          <t>684; 5000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>677; 5627</t>
+          <t>650; 5948</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6153</t>
+          <t>0; 6171</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6078</t>
+          <t>1064; 6173</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>438; 4004</t>
+          <t>422; 4009</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 6214</t>
+          <t>0; 5521</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1004; 7340</t>
+          <t>998; 7262</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2335; 10404</t>
+          <t>2436; 10142</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2105; 8064</t>
+          <t>1978; 8087</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3776; 12916</t>
+          <t>3653; 12548</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6578; 20586</t>
+          <t>7138; 20760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1601; 8301</t>
+          <t>1574; 8258</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3559; 11505</t>
+          <t>3199; 11242</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5470</t>
+          <t>0; 5471</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1075; 8391</t>
+          <t>1095; 9585</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1316; 10867</t>
+          <t>1388; 11341</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4238; 10792</t>
+          <t>4148; 10676</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5012; 15664</t>
+          <t>4988; 15512</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10425; 25328</t>
+          <t>10469; 26020</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4603; 15935</t>
+          <t>4784; 16225</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8538; 19650</t>
+          <t>9058; 20294</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4537</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 1911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>909; 7687</t>
+          <t>960; 8288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>509; 4520</t>
+          <t>505; 4896</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2460; 10905</t>
+          <t>2390; 11039</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12470; 27545</t>
+          <t>12192; 27771</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5965; 17272</t>
+          <t>5761; 17766</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11212; 21051</t>
+          <t>10820; 20424</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3826; 13503</t>
+          <t>3658; 13376</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11989; 27954</t>
+          <t>12454; 29133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8509; 22610</t>
+          <t>8167; 22273</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12453; 23025</t>
+          <t>12497; 22693</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19629; 35641</t>
+          <t>19530; 35602</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20527; 39808</t>
+          <t>20317; 40519</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15195; 34199</t>
+          <t>14641; 33826</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19604; 32765</t>
+          <t>20345; 32969</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19629; 35641</t>
+          <t>19530; 35602</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20527; 39808</t>
+          <t>20317; 40519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15195; 34199</t>
+          <t>14641; 33826</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19672; 32966</t>
+          <t>19719; 32769</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4792; 15366</t>
+          <t>4817; 15129</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9419; 25791</t>
+          <t>8874; 25277</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7267; 19490</t>
+          <t>7062; 18504</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8415; 19972</t>
+          <t>9184; 19914</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28816; 48252</t>
+          <t>28525; 48161</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44562; 71216</t>
+          <t>46208; 72472</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32506; 58447</t>
+          <t>31212; 57263</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44565; 62963</t>
+          <t>44814; 64392</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>36686; 59390</t>
+          <t>37688; 59486</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58121; 89927</t>
+          <t>58267; 88592</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43469; 72335</t>
+          <t>44532; 72981</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56090; 79312</t>
+          <t>56796; 78558</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$familiarvive-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$familiarvive-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>36,71%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,06</t>
+          <t>0,0; 52,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,5; 72,35</t>
+          <t>10,26; 71,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,77</t>
+          <t>0,0; 70,55</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,21</t>
+          <t>0,0; 46,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,62; 51,9</t>
+          <t>10,6; 53,64</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,09</t>
+          <t>0,0; 66,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,81</t>
+          <t>0,0; 81,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,97</t>
+          <t>0,0; 44,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 45,07</t>
+          <t>4,05; 41,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,25</t>
+          <t>0,0; 63,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,33</t>
+          <t>0,0; 60,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 32,26</t>
+          <t>4,66; 33,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,95</t>
+          <t>0,0; 60,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 47,93</t>
+          <t>0,0; 48,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 43,37</t>
+          <t>5,19; 41,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,66</t>
+          <t>0,0; 57,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 84,92</t>
+          <t>14,06; 84,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 22,23</t>
+          <t>2,24; 22,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,77</t>
+          <t>0,0; 53,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 41,23</t>
+          <t>5,62; 41,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,76; 57,31</t>
+          <t>14,04; 58,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 25,47</t>
+          <t>6,8; 25,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,4; 42,6</t>
+          <t>12,73; 44,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,79; 48,84</t>
+          <t>15,47; 48,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 33,49</t>
+          <t>6,35; 33,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 22,24</t>
+          <t>7,18; 23,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,39</t>
+          <t>0,0; 74,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,01; 52,62</t>
+          <t>5,33; 46,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 51,88</t>
+          <t>6,38; 49,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,72; 37,88</t>
+          <t>14,87; 35,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,55; 42,14</t>
+          <t>14,24; 43,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,24; 42,85</t>
+          <t>16,27; 41,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 34,88</t>
+          <t>9,64; 36,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,51; 25,78</t>
+          <t>11,58; 25,1</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,12</t>
+          <t>0,0; 48,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,59 +1287,59 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 32,28</t>
+          <t>3,65; 31,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 26,98</t>
+          <t>2,74; 25,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,85; 63,96</t>
+          <t>13,98; 63,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,66; 42,5</t>
+          <t>17,4; 41,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 49,67</t>
+          <t>13,95; 47,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 24,65</t>
+          <t>13,9; 26,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,3; 48,63</t>
+          <t>13,48; 47,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,92; 34,89</t>
+          <t>14,46; 34,04</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,29; 36,25</t>
+          <t>12,91; 35,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 22,47</t>
+          <t>12,82; 23,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,59; 59,4</t>
+          <t>33,39; 60,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,61; 39,11</t>
+          <t>20,67; 39,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,2; 35,13</t>
+          <t>15,73; 35,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,71; 31,94</t>
+          <t>19,89; 32,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>32,59; 59,4</t>
+          <t>33,39; 60,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,61; 39,11</t>
+          <t>20,67; 39,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,2; 35,13</t>
+          <t>15,73; 35,16</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,72; 31,1</t>
+          <t>19,17; 31,34</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,98; 31,33</t>
+          <t>9,48; 31,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,3; 32,2</t>
+          <t>10,89; 31,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,8; 25,67</t>
+          <t>9,32; 25,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 20,11</t>
+          <t>8,72; 19,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,49; 51,48</t>
+          <t>30,27; 51,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,62; 35,48</t>
+          <t>21,79; 34,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,3; 33,57</t>
+          <t>18,79; 34,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,2; 26,15</t>
+          <t>18,63; 26,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>26,57; 41,94</t>
+          <t>26,23; 41,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,61; 31,33</t>
+          <t>20,98; 31,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,35; 30,07</t>
+          <t>18,46; 29,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,45; 22,75</t>
+          <t>16,8; 23,07</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3442</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3208</t>
+          <t>0; 3123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>555; 4223</t>
+          <t>655; 4554</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4996</t>
+          <t>0; 5279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5365</t>
+          <t>0; 5337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1459; 5999</t>
+          <t>1304; 6597</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1585</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2507</t>
         </is>
       </c>
     </row>
@@ -2140,17 +2140,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4253</t>
+          <t>0; 4364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3969</t>
+          <t>0; 3971</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3586</t>
+          <t>0; 3959</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>393; 3654</t>
+          <t>392; 3983</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6333</t>
+          <t>0; 6271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5831</t>
+          <t>0; 5652</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>599; 5438</t>
+          <t>867; 6146</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4819</t>
         </is>
       </c>
     </row>
@@ -2348,17 +2348,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4324</t>
+          <t>0; 4282</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>684; 5000</t>
+          <t>0; 5015</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>650; 5948</t>
+          <t>740; 5914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6171</t>
+          <t>0; 6099</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1064; 6173</t>
+          <t>1022; 6128</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>422; 4009</t>
+          <t>465; 4602</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5521</t>
+          <t>0; 5604</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>998; 7262</t>
+          <t>991; 7281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2436; 10142</t>
+          <t>2485; 10265</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1978; 8087</t>
+          <t>2381; 8839</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7130</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>14819</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3653; 12548</t>
+          <t>3749; 12980</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7138; 20760</t>
+          <t>6577; 20765</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1574; 8258</t>
+          <t>1566; 8198</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3199; 11242</t>
+          <t>3922; 12861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5471</t>
+          <t>0; 5494</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1095; 9585</t>
+          <t>970; 8434</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1388; 11341</t>
+          <t>1396; 10844</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4148; 10676</t>
+          <t>4482; 10837</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4988; 15512</t>
+          <t>5241; 15905</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10469; 26020</t>
+          <t>9881; 25242</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4784; 16225</t>
+          <t>4484; 16770</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9058; 20294</t>
+          <t>9815; 21280</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15384</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>19135</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4622</t>
+          <t>0; 4935</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2769,59 +2769,59 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>960; 8288</t>
+          <t>937; 8078</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>505; 4896</t>
+          <t>515; 4701</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2390; 11039</t>
+          <t>2413; 11005</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12192; 27771</t>
+          <t>11367; 27397</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5761; 17766</t>
+          <t>4989; 17027</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10820; 20424</t>
+          <t>12490; 23444</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658; 13376</t>
+          <t>3707; 13126</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12454; 29133</t>
+          <t>12070; 28418</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8167; 22273</t>
+          <t>7931; 21992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>12497; 22693</t>
+          <t>13931; 25442</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>28894</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>28894</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19530; 35602</t>
+          <t>20013; 36064</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20317; 40519</t>
+          <t>21414; 40899</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14641; 33826</t>
+          <t>15149; 33861</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20345; 32969</t>
+          <t>22447; 36941</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19530; 35602</t>
+          <t>20013; 36064</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20317; 40519</t>
+          <t>21414; 40899</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14641; 33826</t>
+          <t>15149; 33861</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19719; 32769</t>
+          <t>22050; 36051</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>14260</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>54228</t>
+          <t>59356</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>67497</t>
+          <t>73617</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4817; 15129</t>
+          <t>4577; 15035</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>8874; 25277</t>
+          <t>8549; 24337</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7062; 18504</t>
+          <t>6720; 18714</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9184; 19914</t>
+          <t>9136; 20882</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>28525; 48161</t>
+          <t>28318; 48416</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46208; 72472</t>
+          <t>44505; 70527</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31212; 57263</t>
+          <t>32045; 58835</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>44814; 64392</t>
+          <t>50238; 70408</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37688; 59486</t>
+          <t>37203; 58298</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58267; 88592</t>
+          <t>59338; 90446</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44532; 72981</t>
+          <t>44796; 71750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>56796; 78558</t>
+          <t>62885; 86381</t>
         </is>
       </c>
     </row>
